--- a/latest/BoM/Positional/pedalboard-soundcard-bom.xlsx
+++ b/latest/BoM/Positional/pedalboard-soundcard-bom.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="251">
   <si>
     <t>Row</t>
   </si>
@@ -286,9 +286,6 @@
     <t>LED_SMD</t>
   </si>
   <si>
-    <t>~</t>
-  </si>
-  <si>
     <t>10.0050</t>
   </si>
   <si>
@@ -691,7 +688,7 @@
     <t>KiCad Version:</t>
   </si>
   <si>
-    <t>9.0.7+1</t>
+    <t>10.0.1-10.0.1~ubuntu25.10.1</t>
   </si>
   <si>
     <t>Component Groups:</t>
@@ -1330,7 +1327,7 @@
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="60.7109375" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
     <col min="5" max="5" width="41.7109375" customWidth="1"/>
     <col min="6" max="6" width="24.7109375" customWidth="1"/>
     <col min="7" max="7" width="54.7109375" customWidth="1"/>
@@ -1350,7 +1347,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1375,13 +1372,13 @@
     </row>
     <row r="2" spans="1:23">
       <c r="C2" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F2" s="3">
         <v>21</v>
@@ -1389,41 +1386,41 @@
     </row>
     <row r="3" spans="1:23">
       <c r="C3" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="E3" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="C4" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="E4" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="C5" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1431,13 +1428,13 @@
     </row>
     <row r="6" spans="1:23">
       <c r="C6" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F6" s="3">
         <v>73</v>
@@ -1904,7 +1901,7 @@
         <v>32</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="M14" s="12" t="s">
         <v>24</v>
@@ -1916,13 +1913,13 @@
         <v>52</v>
       </c>
       <c r="P14" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q14" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="R14" s="11" t="s">
         <v>90</v>
-      </c>
-      <c r="R14" s="11" t="s">
-        <v>91</v>
       </c>
       <c r="S14" s="11" t="s">
         <v>40</v>
@@ -1934,36 +1931,36 @@
         <v>42</v>
       </c>
       <c r="V14" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W14" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="W14" s="11" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="45" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>99</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>45</v>
@@ -1975,10 +1972,10 @@
         <v>32</v>
       </c>
       <c r="L15" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="M15" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>101</v>
       </c>
       <c r="N15" s="7" t="s">
         <v>35</v>
@@ -1987,28 +1984,28 @@
         <v>52</v>
       </c>
       <c r="P15" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q15" s="7" t="s">
         <v>102</v>
-      </c>
-      <c r="Q15" s="7" t="s">
-        <v>103</v>
       </c>
       <c r="R15" s="7" t="s">
         <v>55</v>
       </c>
       <c r="S15" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="T15" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="T15" s="7" t="s">
-        <v>105</v>
       </c>
       <c r="U15" s="7" t="s">
         <v>42</v>
       </c>
       <c r="V15" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="W15" s="7" t="s">
         <v>106</v>
-      </c>
-      <c r="W15" s="7" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="30" customHeight="1">
@@ -2019,22 +2016,22 @@
         <v>24</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E16" s="11" t="s">
+      <c r="F16" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>110</v>
-      </c>
       <c r="H16" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>23</v>
@@ -2046,22 +2043,22 @@
         <v>32</v>
       </c>
       <c r="L16" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="M16" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>112</v>
       </c>
       <c r="N16" s="11" t="s">
         <v>61</v>
       </c>
       <c r="O16" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="P16" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="P16" s="11" t="s">
+      <c r="Q16" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="Q16" s="11" t="s">
-        <v>115</v>
       </c>
       <c r="R16" s="11" t="s">
         <v>65</v>
@@ -2070,16 +2067,16 @@
         <v>40</v>
       </c>
       <c r="T16" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U16" s="11" t="s">
         <v>42</v>
       </c>
       <c r="V16" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="W16" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="30" customHeight="1">
@@ -2090,49 +2087,49 @@
         <v>24</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="G17" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="I17" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>123</v>
-      </c>
       <c r="J17" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>32</v>
       </c>
       <c r="L17" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="M17" s="8" t="s">
         <v>124</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>125</v>
       </c>
       <c r="N17" s="7" t="s">
         <v>51</v>
       </c>
       <c r="O17" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="P17" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="P17" s="7" t="s">
+      <c r="Q17" s="7" t="s">
         <v>127</v>
-      </c>
-      <c r="Q17" s="7" t="s">
-        <v>128</v>
       </c>
       <c r="R17" s="7" t="s">
         <v>65</v>
@@ -2147,36 +2144,36 @@
         <v>42</v>
       </c>
       <c r="V17" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="W17" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="W17" s="7" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="30" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>130</v>
-      </c>
       <c r="G18" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="11" t="s">
         <v>121</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>122</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>31</v>
@@ -2188,10 +2185,10 @@
         <v>32</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N18" s="11" t="s">
         <v>35</v>
@@ -2200,10 +2197,10 @@
         <v>36</v>
       </c>
       <c r="P18" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q18" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="Q18" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="R18" s="11" t="s">
         <v>39</v>
@@ -2218,10 +2215,10 @@
         <v>42</v>
       </c>
       <c r="V18" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W18" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="W18" s="11" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:23" ht="30" customHeight="1">
@@ -2232,22 +2229,22 @@
         <v>24</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>135</v>
-      </c>
       <c r="G19" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>122</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>56</v>
@@ -2259,25 +2256,25 @@
         <v>32</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N19" s="7" t="s">
         <v>61</v>
       </c>
       <c r="O19" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="P19" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="P19" s="7" t="s">
+      <c r="Q19" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="Q19" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="R19" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S19" s="7" t="s">
         <v>40</v>
@@ -2289,36 +2286,36 @@
         <v>42</v>
       </c>
       <c r="V19" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="W19" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="W19" s="7" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="30" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>142</v>
-      </c>
       <c r="G20" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20" s="11" t="s">
         <v>121</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>122</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>73</v>
@@ -2330,25 +2327,25 @@
         <v>32</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N20" s="11" t="s">
         <v>51</v>
       </c>
       <c r="O20" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="P20" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="P20" s="11" t="s">
+      <c r="Q20" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="Q20" s="11" t="s">
-        <v>146</v>
-      </c>
       <c r="R20" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S20" s="11" t="s">
         <v>40</v>
@@ -2360,36 +2357,36 @@
         <v>42</v>
       </c>
       <c r="V20" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W20" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="W20" s="11" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="30" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>149</v>
-      </c>
       <c r="G21" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H21" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>122</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>31</v>
@@ -2401,10 +2398,10 @@
         <v>32</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N21" s="7" t="s">
         <v>51</v>
@@ -2413,13 +2410,13 @@
         <v>36</v>
       </c>
       <c r="P21" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q21" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="Q21" s="7" t="s">
-        <v>152</v>
-      </c>
       <c r="R21" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S21" s="7" t="s">
         <v>40</v>
@@ -2431,36 +2428,36 @@
         <v>42</v>
       </c>
       <c r="V21" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="W21" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="W21" s="7" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="45" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="F22" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="G22" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="F22" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="G22" s="11" t="s">
+      <c r="H22" s="11" t="s">
         <v>157</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>158</v>
       </c>
       <c r="I22" s="9" t="s">
         <v>23</v>
@@ -2472,22 +2469,22 @@
         <v>32</v>
       </c>
       <c r="L22" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="M22" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="N22" s="11" t="s">
         <v>61</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P22" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q22" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="Q22" s="11" t="s">
-        <v>162</v>
       </c>
       <c r="R22" s="11" t="s">
         <v>55</v>
@@ -2502,36 +2499,36 @@
         <v>42</v>
       </c>
       <c r="V22" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="W22" s="11" t="s">
         <v>163</v>
-      </c>
-      <c r="W22" s="11" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:23" ht="30" customHeight="1">
       <c r="A23" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="7" t="s">
-        <v>170</v>
-      </c>
       <c r="G23" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>158</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>56</v>
@@ -2543,22 +2540,22 @@
         <v>32</v>
       </c>
       <c r="L23" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="M23" s="8" t="s">
         <v>171</v>
-      </c>
-      <c r="M23" s="8" t="s">
-        <v>172</v>
       </c>
       <c r="N23" s="7" t="s">
         <v>61</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P23" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q23" s="7" t="s">
         <v>173</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>174</v>
       </c>
       <c r="R23" s="7" t="s">
         <v>39</v>
@@ -2573,36 +2570,36 @@
         <v>42</v>
       </c>
       <c r="V23" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="W23" s="7" t="s">
         <v>163</v>
-      </c>
-      <c r="W23" s="7" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="30" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" s="11" t="s">
+      <c r="F24" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="H24" s="11" t="s">
         <v>179</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>180</v>
       </c>
       <c r="I24" s="9" t="s">
         <v>23</v>
@@ -2614,22 +2611,22 @@
         <v>32</v>
       </c>
       <c r="L24" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="M24" s="10" t="s">
         <v>181</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>182</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>51</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P24" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q24" s="11" t="s">
         <v>183</v>
-      </c>
-      <c r="Q24" s="11" t="s">
-        <v>184</v>
       </c>
       <c r="R24" s="11" t="s">
         <v>55</v>
@@ -2644,36 +2641,36 @@
         <v>42</v>
       </c>
       <c r="V24" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="W24" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="W24" s="11" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="30" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="G25" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>191</v>
-      </c>
       <c r="H25" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>23</v>
@@ -2685,22 +2682,22 @@
         <v>32</v>
       </c>
       <c r="L25" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="M25" s="8" t="s">
         <v>192</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>193</v>
       </c>
       <c r="N25" s="7" t="s">
         <v>35</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P25" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q25" s="7" t="s">
         <v>194</v>
-      </c>
-      <c r="Q25" s="7" t="s">
-        <v>195</v>
       </c>
       <c r="R25" s="7" t="s">
         <v>65</v>
@@ -2715,36 +2712,36 @@
         <v>42</v>
       </c>
       <c r="V25" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W25" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="30" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="D26" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E26" s="11" t="s">
+      <c r="F26" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="G26" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="G26" s="11" t="s">
-        <v>201</v>
-      </c>
       <c r="H26" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>23</v>
@@ -2756,22 +2753,22 @@
         <v>32</v>
       </c>
       <c r="L26" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="M26" s="10" t="s">
         <v>202</v>
-      </c>
-      <c r="M26" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="N26" s="11" t="s">
         <v>35</v>
       </c>
       <c r="O26" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P26" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q26" s="11" t="s">
         <v>204</v>
-      </c>
-      <c r="Q26" s="11" t="s">
-        <v>205</v>
       </c>
       <c r="R26" s="11" t="s">
         <v>65</v>
@@ -2786,36 +2783,36 @@
         <v>42</v>
       </c>
       <c r="V26" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="W26" s="11" t="s">
         <v>206</v>
-      </c>
-      <c r="W26" s="11" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="30" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E27" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>210</v>
-      </c>
       <c r="G27" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>23</v>
@@ -2827,22 +2824,22 @@
         <v>32</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N27" s="7" t="s">
         <v>35</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P27" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q27" s="7" t="s">
         <v>212</v>
-      </c>
-      <c r="Q27" s="7" t="s">
-        <v>213</v>
       </c>
       <c r="R27" s="7" t="s">
         <v>65</v>
@@ -2857,10 +2854,10 @@
         <v>42</v>
       </c>
       <c r="V27" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="W27" s="7" t="s">
         <v>206</v>
-      </c>
-      <c r="W27" s="7" t="s">
-        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -2881,7 +2878,8 @@
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="21.7109375" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
     <col min="7" max="7" width="40.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
@@ -2900,7 +2898,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -2925,13 +2923,13 @@
     </row>
     <row r="2" spans="1:23">
       <c r="C2" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F2" s="3">
         <v>21</v>
@@ -2939,41 +2937,41 @@
     </row>
     <row r="3" spans="1:23">
       <c r="C3" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="E3" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="C4" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="E4" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="C5" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -2981,13 +2979,13 @@
     </row>
     <row r="6" spans="1:23">
       <c r="C6" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F6" s="3">
         <v>73</v>
@@ -3072,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>235</v>
-      </c>
       <c r="H9" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J9" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="L9" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="M9" s="8" t="s">
         <v>238</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>239</v>
       </c>
       <c r="N9" s="7" t="s">
         <v>51</v>
@@ -3111,28 +3109,28 @@
         <v>52</v>
       </c>
       <c r="P9" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q9" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="Q9" s="7" t="s">
-        <v>241</v>
-      </c>
       <c r="R9" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S9" s="7" t="s">
         <v>40</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U9" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="V9" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="V9" s="7" t="s">
+      <c r="W9" s="7" t="s">
         <v>243</v>
-      </c>
-      <c r="W9" s="7" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="30" customHeight="1">
@@ -3143,52 +3141,52 @@
         <v>24</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G10" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>121</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>122</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="K10" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="K10" s="9" t="s">
-        <v>237</v>
-      </c>
       <c r="L10" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N10" s="11" t="s">
         <v>61</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P10" s="11" t="s">
         <v>63</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="R10" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S10" s="11" t="s">
         <v>40</v>
@@ -3197,13 +3195,13 @@
         <v>41</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V10" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="W10" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="W10" s="11" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3226,27 +3224,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
